--- a/experiments/completed_experiments/proline_202503051407/protocol/mass_spectrometry/ExperimentTemplate.xlsx
+++ b/experiments/completed_experiments/proline_202503051407/protocol/mass_spectrometry/ExperimentTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/partially_completed/proline_202503051407/protocol/mass_spectrometry/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/completed_experiments/proline_202503051407/protocol/mass_spectrometry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_A135ED0F83B1D9432385B9ACB4E07B79A5845476" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED8CCFF2-A218-9543-B87C-2D30B2A2C82F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A135ED0F83B1D9432335B55F74606F4FA5842000" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="samples" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="164">
   <si>
     <t>Well</t>
   </si>
@@ -93,273 +93,273 @@
     <t>SAMPLE</t>
   </si>
   <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>Growth with 20 mM alanine supplementation, no lactic acid.</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Growth with 10 mM proline supplementation, no lactic acid.</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>Growth with 20 mM alanine supplementation and 50 mM (S)-lactic acid.</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>Growth with 20 mM proline supplementation and 50 mM (S)-lactic acid.</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>Growth with 10 mM proline supplementation and 50 mM (S)-lactic acid.</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>Baseline growth without any supplementation or treatment.</t>
+  </si>
+  <si>
+    <t>H9</t>
+  </si>
+  <si>
+    <t>Growth with 50 mM (S)-lactic acid, no proline supplementation.</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
     <t>D10</t>
   </si>
   <si>
-    <t>Sample</t>
-  </si>
-  <si>
-    <t>Growth with 50 mM (S)-lactic acid, no proline supplementation.</t>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Growth with 20 mM proline supplementation, no lactic acid.</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>F5</t>
   </si>
   <si>
     <t>E7</t>
   </si>
   <si>
-    <t>Growth with 10 mM proline supplementation and 50 mM (S)-lactic acid.</t>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>H8</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>H7</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>G3</t>
   </si>
   <si>
     <t>F7</t>
   </si>
   <si>
-    <t>Baseline growth without any supplementation or treatment.</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>Growth with 20 mM proline supplementation, no lactic acid.</t>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>H10</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>H12</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>B9</t>
   </si>
   <si>
     <t>B10</t>
   </si>
   <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>Growth with 20 mM alanine supplementation, no lactic acid.</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>Growth with 20 mM alanine supplementation and 50 mM (S)-lactic acid.</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>Growth with 10 mM proline supplementation, no lactic acid.</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>Growth with 20 mM proline supplementation and 50 mM (S)-lactic acid.</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>A12</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
     <t>G8</t>
   </si>
   <si>
-    <t>E6</t>
-  </si>
-  <si>
-    <t>H9</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>H3</t>
-  </si>
-  <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
     <t>C12</t>
   </si>
   <si>
-    <t>H7</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>G9</t>
-  </si>
-  <si>
-    <t>G5</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>H5</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>D12</t>
-  </si>
-  <si>
-    <t>A8</t>
-  </si>
-  <si>
-    <t>H8</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>G12</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>E9</t>
-  </si>
-  <si>
-    <t>E11</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>G7</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>D9</t>
-  </si>
-  <si>
-    <t>G6</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>A11</t>
-  </si>
-  <si>
-    <t>H4</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>H12</t>
-  </si>
-  <si>
-    <t>H10</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -514,9 +514,6 @@
   </si>
   <si>
     <t>Skyline output molecule report template (built in and exported from Skyline GUI)</t>
-  </si>
-  <si>
-    <t>SipHeight</t>
   </si>
 </sst>
 </file>
@@ -535,7 +532,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -593,10 +589,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -884,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -1300,15 +1292,15 @@
         <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1332,15 +1324,15 @@
         <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1364,15 +1356,15 @@
         <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1384,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
         <v>14</v>
@@ -1396,15 +1388,15 @@
         <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1416,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G17" t="s">
         <v>14</v>
@@ -1428,15 +1420,15 @@
         <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1448,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" t="s">
         <v>14</v>
@@ -1460,15 +1452,15 @@
         <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1480,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G19" t="s">
         <v>14</v>
@@ -1492,7 +1484,7 @@
         <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1529,10 +1521,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1544,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G21" t="s">
         <v>14</v>
@@ -1556,15 +1548,15 @@
         <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1576,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1588,15 +1580,15 @@
         <v>16</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1608,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G23" t="s">
         <v>14</v>
@@ -1620,15 +1612,15 @@
         <v>16</v>
       </c>
       <c r="J23" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1640,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1652,15 +1644,15 @@
         <v>16</v>
       </c>
       <c r="J24" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1672,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G25" t="s">
         <v>14</v>
@@ -1684,15 +1676,15 @@
         <v>16</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1716,15 +1708,15 @@
         <v>16</v>
       </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1748,15 +1740,15 @@
         <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -1780,15 +1772,15 @@
         <v>16</v>
       </c>
       <c r="J28" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -1800,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G29" t="s">
         <v>14</v>
@@ -1812,15 +1804,15 @@
         <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -1832,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -1844,15 +1836,15 @@
         <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -1864,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
         <v>14</v>
@@ -1876,15 +1868,15 @@
         <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -1896,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
         <v>14</v>
@@ -1908,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -1945,10 +1937,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -1972,12 +1964,12 @@
         <v>16</v>
       </c>
       <c r="J34" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -2004,12 +1996,12 @@
         <v>16</v>
       </c>
       <c r="J35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -2036,12 +2028,12 @@
         <v>16</v>
       </c>
       <c r="J36" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -2068,12 +2060,12 @@
         <v>16</v>
       </c>
       <c r="J37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
         <v>24</v>
@@ -2100,15 +2092,15 @@
         <v>16</v>
       </c>
       <c r="J38" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -2132,15 +2124,15 @@
         <v>16</v>
       </c>
       <c r="J39" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -2152,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G40" t="s">
         <v>14</v>
@@ -2164,15 +2156,15 @@
         <v>16</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -2184,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G41" t="s">
         <v>14</v>
@@ -2196,7 +2188,7 @@
         <v>16</v>
       </c>
       <c r="J41" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -2297,10 +2289,10 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
@@ -2312,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
@@ -2324,7 +2316,7 @@
         <v>16</v>
       </c>
       <c r="J45" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -2361,10 +2353,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
         <v>12</v>
@@ -2388,12 +2380,12 @@
         <v>16</v>
       </c>
       <c r="J47" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B48" t="s">
         <v>24</v>
@@ -2420,12 +2412,12 @@
         <v>16</v>
       </c>
       <c r="J48" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
         <v>24</v>
@@ -2452,12 +2444,12 @@
         <v>16</v>
       </c>
       <c r="J49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
         <v>24</v>
@@ -2489,7 +2481,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
         <v>24</v>
@@ -2516,15 +2508,15 @@
         <v>16</v>
       </c>
       <c r="J51" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
@@ -2548,12 +2540,12 @@
         <v>16</v>
       </c>
       <c r="J52" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
         <v>24</v>
@@ -2580,15 +2572,15 @@
         <v>16</v>
       </c>
       <c r="J53" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
@@ -2612,15 +2604,15 @@
         <v>16</v>
       </c>
       <c r="J54" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
@@ -2632,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G55" t="s">
         <v>14</v>
@@ -2644,15 +2636,15 @@
         <v>16</v>
       </c>
       <c r="J55" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -2664,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
         <v>14</v>
@@ -2676,15 +2668,15 @@
         <v>16</v>
       </c>
       <c r="J56" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
@@ -2696,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G57" t="s">
         <v>14</v>
@@ -2708,15 +2700,15 @@
         <v>16</v>
       </c>
       <c r="J57" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -2728,7 +2720,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
         <v>14</v>
@@ -2740,15 +2732,15 @@
         <v>16</v>
       </c>
       <c r="J58" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
@@ -2760,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G59" t="s">
         <v>14</v>
@@ -2772,15 +2764,15 @@
         <v>16</v>
       </c>
       <c r="J59" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
@@ -2792,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G60" t="s">
         <v>14</v>
@@ -2804,15 +2796,15 @@
         <v>16</v>
       </c>
       <c r="J60" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
@@ -2824,7 +2816,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G61" t="s">
         <v>14</v>
@@ -2836,15 +2828,15 @@
         <v>16</v>
       </c>
       <c r="J61" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
@@ -2856,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G62" t="s">
         <v>14</v>
@@ -2868,15 +2860,15 @@
         <v>16</v>
       </c>
       <c r="J62" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
@@ -2888,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G63" t="s">
         <v>14</v>
@@ -2900,15 +2892,15 @@
         <v>16</v>
       </c>
       <c r="J63" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
@@ -2932,15 +2924,15 @@
         <v>16</v>
       </c>
       <c r="J64" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -2964,12 +2956,12 @@
         <v>16</v>
       </c>
       <c r="J65" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
         <v>24</v>
@@ -2996,15 +2988,15 @@
         <v>16</v>
       </c>
       <c r="J66" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
@@ -3028,15 +3020,15 @@
         <v>16</v>
       </c>
       <c r="J67" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -3048,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G68" t="s">
         <v>14</v>
@@ -3060,15 +3052,15 @@
         <v>16</v>
       </c>
       <c r="J68" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -3080,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G69" t="s">
         <v>14</v>
@@ -3092,15 +3084,15 @@
         <v>16</v>
       </c>
       <c r="J69" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -3112,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G70" t="s">
         <v>14</v>
@@ -3124,15 +3116,15 @@
         <v>16</v>
       </c>
       <c r="J70" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
@@ -3144,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G71" t="s">
         <v>14</v>
@@ -3156,15 +3148,15 @@
         <v>16</v>
       </c>
       <c r="J71" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -3188,15 +3180,15 @@
         <v>16</v>
       </c>
       <c r="J72" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
@@ -3220,12 +3212,12 @@
         <v>16</v>
       </c>
       <c r="J73" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B74" t="s">
         <v>24</v>
@@ -3252,12 +3244,12 @@
         <v>16</v>
       </c>
       <c r="J74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
         <v>24</v>
@@ -3284,12 +3276,12 @@
         <v>16</v>
       </c>
       <c r="J75" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B76" t="s">
         <v>24</v>
@@ -3316,15 +3308,15 @@
         <v>16</v>
       </c>
       <c r="J76" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -3348,15 +3340,15 @@
         <v>16</v>
       </c>
       <c r="J77" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -3368,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G78" t="s">
         <v>14</v>
@@ -3380,15 +3372,15 @@
         <v>16</v>
       </c>
       <c r="J78" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -3400,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G79" t="s">
         <v>14</v>
@@ -3412,15 +3404,15 @@
         <v>16</v>
       </c>
       <c r="J79" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
         <v>12</v>
@@ -3432,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G80" t="s">
         <v>14</v>
@@ -3444,7 +3436,7 @@
         <v>16</v>
       </c>
       <c r="J80" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
@@ -3513,10 +3505,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
@@ -3528,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G83" t="s">
         <v>14</v>
@@ -3540,15 +3532,15 @@
         <v>16</v>
       </c>
       <c r="J83" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
@@ -3560,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
@@ -3572,15 +3564,15 @@
         <v>16</v>
       </c>
       <c r="J84" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C85" t="s">
         <v>12</v>
@@ -3604,15 +3596,15 @@
         <v>16</v>
       </c>
       <c r="J85" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -3636,12 +3628,12 @@
         <v>16</v>
       </c>
       <c r="J86" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B87" t="s">
         <v>24</v>
@@ -3668,12 +3660,12 @@
         <v>16</v>
       </c>
       <c r="J87" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B88" t="s">
         <v>24</v>
@@ -3700,12 +3692,12 @@
         <v>16</v>
       </c>
       <c r="J88" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B89" t="s">
         <v>24</v>
@@ -3732,15 +3724,15 @@
         <v>16</v>
       </c>
       <c r="J89" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C90" t="s">
         <v>12</v>
@@ -3764,12 +3756,12 @@
         <v>16</v>
       </c>
       <c r="J90" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B91" t="s">
         <v>24</v>
@@ -3796,12 +3788,12 @@
         <v>16</v>
       </c>
       <c r="J91" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B92" t="s">
         <v>24</v>
@@ -3828,15 +3820,15 @@
         <v>16</v>
       </c>
       <c r="J92" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -3860,15 +3852,15 @@
         <v>16</v>
       </c>
       <c r="J93" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
         <v>12</v>
@@ -3880,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G94" t="s">
         <v>14</v>
@@ -3892,15 +3884,15 @@
         <v>16</v>
       </c>
       <c r="J94" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C95" t="s">
         <v>12</v>
@@ -3912,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G95" t="s">
         <v>14</v>
@@ -3924,15 +3916,15 @@
         <v>16</v>
       </c>
       <c r="J95" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
         <v>12</v>
@@ -3944,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G96" t="s">
         <v>14</v>
@@ -3956,7 +3948,7 @@
         <v>16</v>
       </c>
       <c r="J96" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
@@ -3993,10 +3985,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C98" t="s">
         <v>12</v>
@@ -4008,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G98" t="s">
         <v>14</v>
@@ -4020,15 +4012,15 @@
         <v>16</v>
       </c>
       <c r="J98" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
         <v>12</v>
@@ -4040,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G99" t="s">
         <v>14</v>
@@ -4052,15 +4044,15 @@
         <v>16</v>
       </c>
       <c r="J99" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="B100" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
@@ -4072,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G100" t="s">
         <v>14</v>
@@ -4084,15 +4076,15 @@
         <v>16</v>
       </c>
       <c r="J100" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
@@ -4104,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G101" t="s">
         <v>14</v>
@@ -4116,15 +4108,15 @@
         <v>16</v>
       </c>
       <c r="J101" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
@@ -4148,15 +4140,15 @@
         <v>16</v>
       </c>
       <c r="J102" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C103" t="s">
         <v>12</v>
@@ -4180,12 +4172,12 @@
         <v>16</v>
       </c>
       <c r="J103" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B104" t="s">
         <v>24</v>
@@ -4212,12 +4204,12 @@
         <v>16</v>
       </c>
       <c r="J104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B105" t="s">
         <v>24</v>
@@ -4244,15 +4236,15 @@
         <v>16</v>
       </c>
       <c r="J105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
@@ -4276,15 +4268,15 @@
         <v>16</v>
       </c>
       <c r="J106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C107" t="s">
         <v>12</v>
@@ -4296,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G107" t="s">
         <v>14</v>
@@ -4308,15 +4300,15 @@
         <v>16</v>
       </c>
       <c r="J107" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C108" t="s">
         <v>12</v>
@@ -4328,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G108" t="s">
         <v>14</v>
@@ -4340,15 +4332,15 @@
         <v>16</v>
       </c>
       <c r="J108" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C109" t="s">
         <v>12</v>
@@ -4360,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G109" t="s">
         <v>14</v>
@@ -4372,15 +4364,15 @@
         <v>16</v>
       </c>
       <c r="J109" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C110" t="s">
         <v>12</v>
@@ -4392,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G110" t="s">
         <v>14</v>
@@ -4404,15 +4396,15 @@
         <v>16</v>
       </c>
       <c r="J110" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C111" t="s">
         <v>12</v>
@@ -4436,15 +4428,15 @@
         <v>16</v>
       </c>
       <c r="J111" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C112" t="s">
         <v>12</v>
@@ -4468,12 +4460,12 @@
         <v>16</v>
       </c>
       <c r="J112" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B113" t="s">
         <v>24</v>
@@ -4500,12 +4492,12 @@
         <v>16</v>
       </c>
       <c r="J113" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B114" t="s">
         <v>24</v>
@@ -4532,15 +4524,15 @@
         <v>16</v>
       </c>
       <c r="J114" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C115" t="s">
         <v>12</v>
@@ -4564,15 +4556,15 @@
         <v>16</v>
       </c>
       <c r="J115" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
@@ -4584,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G116" t="s">
         <v>14</v>
@@ -4596,15 +4588,15 @@
         <v>16</v>
       </c>
       <c r="J116" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C117" t="s">
         <v>12</v>
@@ -4616,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G117" t="s">
         <v>14</v>
@@ -4628,15 +4620,15 @@
         <v>16</v>
       </c>
       <c r="J117" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C118" t="s">
         <v>12</v>
@@ -4648,7 +4640,7 @@
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G118" t="s">
         <v>14</v>
@@ -4660,15 +4652,15 @@
         <v>16</v>
       </c>
       <c r="J118" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B119" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C119" t="s">
         <v>12</v>
@@ -4680,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G119" t="s">
         <v>14</v>
@@ -4692,7 +4684,7 @@
         <v>16</v>
       </c>
       <c r="J119" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
@@ -4729,10 +4721,10 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B121" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C121" t="s">
         <v>12</v>
@@ -4744,7 +4736,7 @@
         <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G121" t="s">
         <v>14</v>
@@ -4756,15 +4748,15 @@
         <v>16</v>
       </c>
       <c r="J121" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C122" t="s">
         <v>12</v>
@@ -4776,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G122" t="s">
         <v>14</v>
@@ -4788,15 +4780,15 @@
         <v>16</v>
       </c>
       <c r="J122" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="B123" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C123" t="s">
         <v>12</v>
@@ -4808,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G123" t="s">
         <v>14</v>
@@ -4820,15 +4812,15 @@
         <v>16</v>
       </c>
       <c r="J123" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B124" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C124" t="s">
         <v>12</v>
@@ -4852,15 +4844,15 @@
         <v>16</v>
       </c>
       <c r="J124" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C125" t="s">
         <v>12</v>
@@ -4884,12 +4876,12 @@
         <v>16</v>
       </c>
       <c r="J125" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B126" t="s">
         <v>24</v>
@@ -4916,12 +4908,12 @@
         <v>16</v>
       </c>
       <c r="J126" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B127" t="s">
         <v>24</v>
@@ -4948,15 +4940,15 @@
         <v>16</v>
       </c>
       <c r="J127" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C128" t="s">
         <v>12</v>
@@ -4980,12 +4972,12 @@
         <v>16</v>
       </c>
       <c r="J128" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B129" t="s">
         <v>24</v>
@@ -5012,12 +5004,12 @@
         <v>16</v>
       </c>
       <c r="J129" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B130" t="s">
         <v>24</v>
@@ -5044,12 +5036,12 @@
         <v>16</v>
       </c>
       <c r="J130" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B131" t="s">
         <v>24</v>
@@ -5076,15 +5068,15 @@
         <v>16</v>
       </c>
       <c r="J131" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C132" t="s">
         <v>12</v>
@@ -5108,15 +5100,15 @@
         <v>16</v>
       </c>
       <c r="J132" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="B133" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C133" t="s">
         <v>12</v>
@@ -5128,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G133" t="s">
         <v>14</v>
@@ -5140,15 +5132,15 @@
         <v>16</v>
       </c>
       <c r="J133" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C134" t="s">
         <v>12</v>
@@ -5160,7 +5152,7 @@
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G134" t="s">
         <v>14</v>
@@ -5172,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="J134" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
@@ -5241,10 +5233,10 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C137" t="s">
         <v>12</v>
@@ -5256,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G137" t="s">
         <v>14</v>
@@ -5268,15 +5260,15 @@
         <v>16</v>
       </c>
       <c r="J137" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
         <v>12</v>
@@ -5288,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G138" t="s">
         <v>14</v>
@@ -5300,15 +5292,15 @@
         <v>16</v>
       </c>
       <c r="J138" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C139" t="s">
         <v>12</v>
@@ -5320,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G139" t="s">
         <v>14</v>
@@ -5332,15 +5324,15 @@
         <v>16</v>
       </c>
       <c r="J139" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C140" t="s">
         <v>12</v>
@@ -5364,15 +5356,15 @@
         <v>16</v>
       </c>
       <c r="J140" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="B141" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C141" t="s">
         <v>12</v>
@@ -5396,12 +5388,12 @@
         <v>16</v>
       </c>
       <c r="J141" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B142" t="s">
         <v>24</v>
@@ -5428,12 +5420,12 @@
         <v>16</v>
       </c>
       <c r="J142" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B143" t="s">
         <v>24</v>
@@ -5460,12 +5452,12 @@
         <v>16</v>
       </c>
       <c r="J143" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B144" t="s">
         <v>24</v>
@@ -5492,15 +5484,15 @@
         <v>16</v>
       </c>
       <c r="J144" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="B145" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
         <v>12</v>
@@ -5524,15 +5516,15 @@
         <v>16</v>
       </c>
       <c r="J145" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="B146" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C146" t="s">
         <v>12</v>
@@ -5544,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G146" t="s">
         <v>14</v>
@@ -5556,15 +5548,15 @@
         <v>16</v>
       </c>
       <c r="J146" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C147" t="s">
         <v>12</v>
@@ -5576,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G147" t="s">
         <v>14</v>
@@ -5588,15 +5580,15 @@
         <v>16</v>
       </c>
       <c r="J147" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C148" t="s">
         <v>12</v>
@@ -5608,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G148" t="s">
         <v>14</v>
@@ -5620,15 +5612,15 @@
         <v>16</v>
       </c>
       <c r="J148" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C149" t="s">
         <v>12</v>
@@ -5640,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G149" t="s">
         <v>14</v>
@@ -5652,15 +5644,15 @@
         <v>16</v>
       </c>
       <c r="J149" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="B150" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C150" t="s">
         <v>12</v>
@@ -5684,15 +5676,15 @@
         <v>16</v>
       </c>
       <c r="J150" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="B151" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C151" t="s">
         <v>12</v>
@@ -5716,12 +5708,12 @@
         <v>16</v>
       </c>
       <c r="J151" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B152" t="s">
         <v>24</v>
@@ -5753,10 +5745,10 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="B153" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C153" t="s">
         <v>12</v>
@@ -5780,15 +5772,15 @@
         <v>16</v>
       </c>
       <c r="J153" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B154" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C154" t="s">
         <v>12</v>
@@ -5800,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G154" t="s">
         <v>14</v>
@@ -5812,15 +5804,15 @@
         <v>16</v>
       </c>
       <c r="J154" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="B155" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C155" t="s">
         <v>12</v>
@@ -5832,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G155" t="s">
         <v>14</v>
@@ -5844,15 +5836,15 @@
         <v>16</v>
       </c>
       <c r="J155" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C156" t="s">
         <v>12</v>
@@ -5864,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G156" t="s">
         <v>14</v>
@@ -5876,15 +5868,15 @@
         <v>16</v>
       </c>
       <c r="J156" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C157" t="s">
         <v>12</v>
@@ -5896,7 +5888,7 @@
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G157" t="s">
         <v>14</v>
@@ -5908,38 +5900,870 @@
         <v>16</v>
       </c>
       <c r="J157" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>20</v>
+      </c>
+      <c r="B158" t="s">
+        <v>21</v>
+      </c>
+      <c r="C158" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" t="s">
+        <v>14</v>
+      </c>
+      <c r="H158" t="s">
+        <v>15</v>
+      </c>
+      <c r="I158" t="s">
+        <v>16</v>
+      </c>
+      <c r="J158" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
         <v>10</v>
       </c>
-      <c r="B158" t="s">
-        <v>18</v>
-      </c>
-      <c r="C158" t="s">
-        <v>12</v>
-      </c>
-      <c r="D158">
-        <v>1</v>
-      </c>
-      <c r="E158">
-        <v>1</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="B159" t="s">
+        <v>18</v>
+      </c>
+      <c r="C159" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159" t="s">
         <v>19</v>
       </c>
-      <c r="G158" t="s">
-        <v>14</v>
-      </c>
-      <c r="H158" t="s">
-        <v>15</v>
-      </c>
-      <c r="I158" t="s">
-        <v>16</v>
-      </c>
-      <c r="J158" t="s">
+      <c r="G159" t="s">
+        <v>14</v>
+      </c>
+      <c r="H159" t="s">
+        <v>15</v>
+      </c>
+      <c r="I159" t="s">
+        <v>16</v>
+      </c>
+      <c r="J159" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160" t="s">
+        <v>18</v>
+      </c>
+      <c r="C160" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+      <c r="F160" t="s">
+        <v>19</v>
+      </c>
+      <c r="G160" t="s">
+        <v>14</v>
+      </c>
+      <c r="H160" t="s">
+        <v>15</v>
+      </c>
+      <c r="I160" t="s">
+        <v>16</v>
+      </c>
+      <c r="J160" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>10</v>
+      </c>
+      <c r="B161" t="s">
+        <v>18</v>
+      </c>
+      <c r="C161" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161">
+        <v>1</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161" t="s">
+        <v>14</v>
+      </c>
+      <c r="H161" t="s">
+        <v>15</v>
+      </c>
+      <c r="I161" t="s">
+        <v>16</v>
+      </c>
+      <c r="J161" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>10</v>
+      </c>
+      <c r="B162" t="s">
+        <v>18</v>
+      </c>
+      <c r="C162" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162">
+        <v>1</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+      <c r="F162" t="s">
+        <v>19</v>
+      </c>
+      <c r="G162" t="s">
+        <v>14</v>
+      </c>
+      <c r="H162" t="s">
+        <v>15</v>
+      </c>
+      <c r="I162" t="s">
+        <v>16</v>
+      </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>20</v>
+      </c>
+      <c r="B163" t="s">
+        <v>21</v>
+      </c>
+      <c r="C163" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163">
+        <v>1</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" t="s">
+        <v>14</v>
+      </c>
+      <c r="H163" t="s">
+        <v>15</v>
+      </c>
+      <c r="I163" t="s">
+        <v>16</v>
+      </c>
+      <c r="J163" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>20</v>
+      </c>
+      <c r="B164" t="s">
+        <v>21</v>
+      </c>
+      <c r="C164" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164">
+        <v>1</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" t="s">
+        <v>14</v>
+      </c>
+      <c r="H164" t="s">
+        <v>15</v>
+      </c>
+      <c r="I164" t="s">
+        <v>16</v>
+      </c>
+      <c r="J164" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>104</v>
+      </c>
+      <c r="B165" t="s">
+        <v>24</v>
+      </c>
+      <c r="C165" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165">
+        <v>1</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+      <c r="F165" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" t="s">
+        <v>14</v>
+      </c>
+      <c r="H165" t="s">
+        <v>15</v>
+      </c>
+      <c r="I165" t="s">
+        <v>16</v>
+      </c>
+      <c r="J165" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>105</v>
+      </c>
+      <c r="B166" t="s">
+        <v>24</v>
+      </c>
+      <c r="C166" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166">
+        <v>1</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+      <c r="F166" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" t="s">
+        <v>14</v>
+      </c>
+      <c r="H166" t="s">
+        <v>15</v>
+      </c>
+      <c r="I166" t="s">
+        <v>16</v>
+      </c>
+      <c r="J166" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>106</v>
+      </c>
+      <c r="B167" t="s">
+        <v>24</v>
+      </c>
+      <c r="C167" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+      <c r="F167" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" t="s">
+        <v>14</v>
+      </c>
+      <c r="H167" t="s">
+        <v>15</v>
+      </c>
+      <c r="I167" t="s">
+        <v>16</v>
+      </c>
+      <c r="J167" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>107</v>
+      </c>
+      <c r="B168" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168">
+        <v>1</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+      <c r="F168" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" t="s">
+        <v>14</v>
+      </c>
+      <c r="H168" t="s">
+        <v>15</v>
+      </c>
+      <c r="I168" t="s">
+        <v>16</v>
+      </c>
+      <c r="J168" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>108</v>
+      </c>
+      <c r="B169" t="s">
+        <v>24</v>
+      </c>
+      <c r="C169" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169">
+        <v>1</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+      <c r="F169" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" t="s">
+        <v>14</v>
+      </c>
+      <c r="H169" t="s">
+        <v>15</v>
+      </c>
+      <c r="I169" t="s">
+        <v>16</v>
+      </c>
+      <c r="J169" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>109</v>
+      </c>
+      <c r="B170" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170">
+        <v>1</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+      <c r="F170" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>14</v>
+      </c>
+      <c r="H170" t="s">
+        <v>15</v>
+      </c>
+      <c r="I170" t="s">
+        <v>16</v>
+      </c>
+      <c r="J170" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>20</v>
+      </c>
+      <c r="B171" t="s">
+        <v>21</v>
+      </c>
+      <c r="C171" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+      <c r="F171" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>14</v>
+      </c>
+      <c r="H171" t="s">
+        <v>15</v>
+      </c>
+      <c r="I171" t="s">
+        <v>16</v>
+      </c>
+      <c r="J171" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>10</v>
+      </c>
+      <c r="B172" t="s">
+        <v>18</v>
+      </c>
+      <c r="C172" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172">
+        <v>1</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172" t="s">
+        <v>19</v>
+      </c>
+      <c r="G172" t="s">
+        <v>14</v>
+      </c>
+      <c r="H172" t="s">
+        <v>15</v>
+      </c>
+      <c r="I172" t="s">
+        <v>16</v>
+      </c>
+      <c r="J172" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>10</v>
+      </c>
+      <c r="B173" t="s">
+        <v>18</v>
+      </c>
+      <c r="C173" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173">
+        <v>1</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+      <c r="F173" t="s">
+        <v>19</v>
+      </c>
+      <c r="G173" t="s">
+        <v>14</v>
+      </c>
+      <c r="H173" t="s">
+        <v>15</v>
+      </c>
+      <c r="I173" t="s">
+        <v>16</v>
+      </c>
+      <c r="J173" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>10</v>
+      </c>
+      <c r="B174" t="s">
+        <v>18</v>
+      </c>
+      <c r="C174" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+      <c r="F174" t="s">
+        <v>19</v>
+      </c>
+      <c r="G174" t="s">
+        <v>14</v>
+      </c>
+      <c r="H174" t="s">
+        <v>15</v>
+      </c>
+      <c r="I174" t="s">
+        <v>16</v>
+      </c>
+      <c r="J174" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>10</v>
+      </c>
+      <c r="B175" t="s">
+        <v>18</v>
+      </c>
+      <c r="C175" t="s">
+        <v>12</v>
+      </c>
+      <c r="D175">
+        <v>1</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+      <c r="F175" t="s">
+        <v>19</v>
+      </c>
+      <c r="G175" t="s">
+        <v>14</v>
+      </c>
+      <c r="H175" t="s">
+        <v>15</v>
+      </c>
+      <c r="I175" t="s">
+        <v>16</v>
+      </c>
+      <c r="J175" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>20</v>
+      </c>
+      <c r="B176" t="s">
+        <v>21</v>
+      </c>
+      <c r="C176" t="s">
+        <v>12</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+      <c r="F176" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>14</v>
+      </c>
+      <c r="H176" t="s">
+        <v>15</v>
+      </c>
+      <c r="I176" t="s">
+        <v>16</v>
+      </c>
+      <c r="J176" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>20</v>
+      </c>
+      <c r="B177" t="s">
+        <v>21</v>
+      </c>
+      <c r="C177" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+      <c r="F177" t="s">
+        <v>22</v>
+      </c>
+      <c r="G177" t="s">
+        <v>14</v>
+      </c>
+      <c r="H177" t="s">
+        <v>15</v>
+      </c>
+      <c r="I177" t="s">
+        <v>16</v>
+      </c>
+      <c r="J177" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>110</v>
+      </c>
+      <c r="B178" t="s">
+        <v>24</v>
+      </c>
+      <c r="C178" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178">
+        <v>1</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" t="s">
+        <v>14</v>
+      </c>
+      <c r="H178" t="s">
+        <v>15</v>
+      </c>
+      <c r="I178" t="s">
+        <v>16</v>
+      </c>
+      <c r="J178" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>111</v>
+      </c>
+      <c r="B179" t="s">
+        <v>24</v>
+      </c>
+      <c r="C179" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179" t="s">
+        <v>14</v>
+      </c>
+      <c r="H179" t="s">
+        <v>15</v>
+      </c>
+      <c r="I179" t="s">
+        <v>16</v>
+      </c>
+      <c r="J179" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>20</v>
+      </c>
+      <c r="B180" t="s">
+        <v>21</v>
+      </c>
+      <c r="C180" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+      <c r="F180" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" t="s">
+        <v>14</v>
+      </c>
+      <c r="H180" t="s">
+        <v>15</v>
+      </c>
+      <c r="I180" t="s">
+        <v>16</v>
+      </c>
+      <c r="J180" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>10</v>
+      </c>
+      <c r="B181" t="s">
+        <v>18</v>
+      </c>
+      <c r="C181" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+      <c r="F181" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181" t="s">
+        <v>14</v>
+      </c>
+      <c r="H181" t="s">
+        <v>15</v>
+      </c>
+      <c r="I181" t="s">
+        <v>16</v>
+      </c>
+      <c r="J181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>10</v>
+      </c>
+      <c r="B182" t="s">
+        <v>18</v>
+      </c>
+      <c r="C182" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+      <c r="F182" t="s">
+        <v>19</v>
+      </c>
+      <c r="G182" t="s">
+        <v>14</v>
+      </c>
+      <c r="H182" t="s">
+        <v>15</v>
+      </c>
+      <c r="I182" t="s">
+        <v>16</v>
+      </c>
+      <c r="J182" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>10</v>
+      </c>
+      <c r="B183" t="s">
+        <v>18</v>
+      </c>
+      <c r="C183" t="s">
+        <v>12</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183" t="s">
+        <v>14</v>
+      </c>
+      <c r="H183" t="s">
+        <v>15</v>
+      </c>
+      <c r="I183" t="s">
+        <v>16</v>
+      </c>
+      <c r="J183" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184" t="s">
+        <v>18</v>
+      </c>
+      <c r="C184" t="s">
+        <v>12</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184" t="s">
+        <v>19</v>
+      </c>
+      <c r="G184" t="s">
+        <v>14</v>
+      </c>
+      <c r="H184" t="s">
+        <v>15</v>
+      </c>
+      <c r="I184" t="s">
+        <v>16</v>
+      </c>
+      <c r="J184" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5950,12 +6774,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -5971,15 +6791,15 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5987,15 +6807,15 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6003,63 +6823,63 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" t="b">
+        <v>118</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" t="b">
+        <v>119</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" t="b">
+        <v>120</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" t="b">
-        <v>0</v>
+        <v>121</v>
+      </c>
+      <c r="B9">
+        <v>1.25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B10">
-        <v>1.25</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11">
-        <v>0.01</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12">
-        <v>1.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13">
         <v>-1</v>
@@ -6067,7 +6887,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14">
         <v>-1</v>
@@ -6075,7 +6895,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B15">
         <v>-1</v>
@@ -6083,7 +6903,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16">
         <v>-1</v>
@@ -6091,7 +6911,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B17">
         <v>-1</v>
@@ -6099,7 +6919,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18">
         <v>-1</v>
@@ -6107,15 +6927,21 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B20">
         <v>100</v>
@@ -6129,7 +6955,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B21">
         <v>100</v>
@@ -6143,112 +6969,98 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B22">
-        <v>100</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" t="b">
+        <v>135</v>
+      </c>
+      <c r="B23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" t="b">
+        <v>136</v>
+      </c>
+      <c r="B24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" t="b">
+        <v>137</v>
+      </c>
+      <c r="B25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" t="b">
+        <v>138</v>
+      </c>
+      <c r="B26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>138</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="B27" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>139</v>
-      </c>
-      <c r="B28" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="B28">
+        <v>10000</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>141</v>
-      </c>
-      <c r="B29">
-        <v>10000</v>
+        <v>142</v>
+      </c>
+      <c r="B29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>142</v>
-      </c>
-      <c r="B30" t="s">
-        <v>143</v>
-      </c>
-      <c r="C30" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" t="s">
-        <v>146</v>
-      </c>
-      <c r="F30" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
         <v>148</v>
       </c>
-      <c r="B31">
+      <c r="B30">
         <v>600</v>
       </c>
-      <c r="C31">
-        <v>4000</v>
-      </c>
-      <c r="D31">
+      <c r="C30">
+        <v>3000</v>
+      </c>
+      <c r="D30">
         <v>0</v>
       </c>
-      <c r="E31">
-        <v>7000</v>
-      </c>
-      <c r="F31">
-        <v>1500</v>
+      <c r="E30">
+        <v>3000</v>
+      </c>
+      <c r="F30">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -6260,10 +7072,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="68.6640625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
